--- a/外部API連携仕様書.xlsx
+++ b/外部API連携仕様書.xlsx
@@ -516,7 +516,7 @@
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Book\BookController@searchIsbn（GET /books/isbn/{isbn}、ログイン必須）
-Laravel の HTTPクライアント（Http::get）で呼び出す。タイムアウト・リトライは個別に設定していない（デフォルトのまま）</t>
+Laravel の HTTPクライアント（Http::get）で呼び出す。タイムアウトは10秒（Http::timeout(10)）。リトライは設定していない</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>エラーメッセージを表示（赤）</t>
+          <t>エラーメッセージを表示（赤）。入力欄は変更しない</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>エラーメッセージを表示（赤）</t>
+          <t>エラーメッセージを表示（赤）。入力欄は変更しない</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>エラーメッセージを表示（赤）</t>
+          <t>エラーメッセージを表示（赤）。入力欄は変更しない</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Google Books API がエラーを返した（HTTPステータス 4xx・5xx）</t>
+          <t>Google Books API がエラーを返した（HTTPステータス 4xx・5xx）、または接続できない・タイムアウトした</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>エラーメッセージを表示（赤）</t>
+          <t>エラーメッセージを表示（赤）。入力欄は変更しない</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Book\BookController@searchIsbn（$response-&gt;failed()）</t>
+          <t>Book\BookController@searchIsbn（$response-&gt;failed()、または ConnectionException を捕捉）</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>エラーメッセージを表示（赤）</t>
+          <t>エラーメッセージを表示（赤）。入力欄は変更しない</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1296,12 +1296,44 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>「通信エラーが発生しました。」を表示（赤）</t>
+          <t>「通信エラーが発生しました。」を表示（赤）。入力欄は変更しない</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>books/create.blade.php（JavaScript）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>サーバーが error キーのないエラーを返した（ログイン切れの401、想定外の500など）</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>401・500など</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>{"message": "..."}（Laravel 標準の形式）</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>「書籍情報の取得中にエラーが発生しました。」を表示（赤）。入力欄は変更しない</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>books/create.blade.php（JavaScript。response.ok で判定）</t>
         </is>
       </c>
     </row>
